--- a/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_901_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15983,7 +15983,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17248,7 +17248,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18260,7 +18260,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL NOGAL (IED)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_901_CALIFICADO.xlsx
@@ -1191,9 +1191,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1444,9 +1444,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1697,9 +1697,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1950,9 +1950,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -2709,9 +2709,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -2962,9 +2962,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -3468,9 +3468,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -3721,9 +3721,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -4986,9 +4986,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -5492,9 +5492,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -5998,9 +5998,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -6504,9 +6504,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -6757,9 +6757,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB25" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -7010,9 +7010,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB26" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -7263,9 +7263,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB27" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -7516,9 +7516,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB28" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -7765,9 +7765,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB29" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -8271,9 +8271,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -8524,9 +8524,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB32" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -9532,9 +9532,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB36" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -10038,9 +10038,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB38" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -10291,9 +10291,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB39" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -10544,9 +10544,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB40" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-EL-NOGAL-(IED)-PRUEBA_901_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,11 +6036,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6132,7 +6044,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,11 +6285,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6385,7 +6293,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,11 +6534,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6638,7 +6542,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6879,11 +6783,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -6891,7 +6791,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7132,11 +7032,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7144,7 +7040,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7385,11 +7281,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7397,7 +7289,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7646,7 +7534,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -7899,7 +7783,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8152,7 +8032,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8405,7 +8281,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8642,11 +8518,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8654,7 +8526,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8895,11 +8767,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -8907,7 +8775,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9148,11 +9016,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9160,7 +9024,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9401,11 +9265,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9413,7 +9273,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9654,11 +9514,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9666,7 +9522,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9907,11 +9763,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -9919,7 +9771,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10160,11 +10012,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10172,7 +10020,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10413,11 +10261,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10425,7 +10269,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10666,11 +10510,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10678,7 +10518,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10919,11 +10759,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -10931,7 +10767,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11168,11 +11004,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11180,7 +11012,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11421,11 +11253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11433,7 +11261,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11670,11 +11498,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11682,7 +11506,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11923,11 +11747,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -11935,7 +11755,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12176,11 +11996,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12188,7 +12004,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12429,11 +12245,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12441,7 +12253,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12682,11 +12494,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12694,7 +12502,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12935,11 +12743,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -12947,7 +12751,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13188,11 +12992,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13200,7 +13000,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13441,11 +13241,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13453,7 +13249,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13694,11 +13490,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13706,7 +13498,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13947,11 +13739,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -13959,7 +13747,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14200,11 +13988,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14212,7 +13996,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14453,11 +14237,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14465,7 +14245,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14706,11 +14486,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14718,7 +14494,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14959,11 +14735,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -14971,7 +14743,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15212,11 +14984,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15224,7 +14992,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15465,11 +15233,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15477,7 +15241,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15718,11 +15482,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15730,7 +15490,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15971,11 +15731,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -15983,7 +15739,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16224,11 +15980,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16236,7 +15988,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16477,11 +16229,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16489,7 +16237,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16730,11 +16478,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16742,7 +16486,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16983,11 +16727,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -16995,7 +16735,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17236,11 +16976,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -17248,7 +16984,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17489,11 +17225,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -17501,7 +17233,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17742,11 +17474,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -17754,7 +17482,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17995,11 +17723,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -18007,7 +17731,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18248,11 +17972,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -18260,7 +17980,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18501,11 +18221,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -18513,7 +18229,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18754,11 +18470,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -18766,7 +18478,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -19007,11 +18719,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -19019,7 +18727,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19260,11 +18968,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -19272,7 +18976,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19513,11 +19217,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -19525,7 +19225,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19766,11 +19466,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -19778,7 +19474,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -20019,11 +19715,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -20031,7 +19723,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20272,11 +19964,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001800635</t>
@@ -20284,7 +19972,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL NOGAL (IED)</t>
+          <t>COLEGIO EL NOGAL (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
